--- a/Results/final_holdout_test_results_PROGRESS.xlsx
+++ b/Results/final_holdout_test_results_PROGRESS.xlsx
@@ -14,11 +14,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+  <si>
+    <t>Run_ID</t>
+  </si>
   <si>
     <t>Model</t>
   </si>
   <si>
+    <t>Best_Params</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>Accuracy</t>
   </si>
   <si>
@@ -34,10 +43,10 @@
     <t>ROC_AUC</t>
   </si>
   <si>
-    <t>Brier_Score</t>
-  </si>
-  <si>
-    <t>Best_Params</t>
+    <t>Brier</t>
+  </si>
+  <si>
+    <t>e1436f8674227c16</t>
   </si>
   <si>
     <t>Logistic Regression</t>
@@ -64,28 +73,28 @@
     <t>XGBoost</t>
   </si>
   <si>
-    <t>{'model__C': 100, 'model__penalty': 'l2'}</t>
-  </si>
-  <si>
-    <t>{'model__n_neighbors': 11, 'model__p': 1, 'model__weights': 'distance'}</t>
-  </si>
-  <si>
-    <t>{'model__C': 0.1, 'model__gamma': 'auto', 'model__kernel': 'rbf'}</t>
-  </si>
-  <si>
-    <t>{'model__max_depth': 3, 'model__min_samples_leaf': 4, 'model__min_samples_split': 2}</t>
-  </si>
-  <si>
-    <t>{'model__max_depth': 5, 'model__max_features': 'sqrt', 'model__min_samples_leaf': 2, 'model__min_samples_split': 5, 'model__n_estimators': 500}</t>
-  </si>
-  <si>
-    <t>{'model__alpha': 1}</t>
-  </si>
-  <si>
-    <t>{'model__learning_rate': 0.01, 'model__max_depth': -1, 'model__n_estimators': 300, 'model__num_leaves': 7, 'model__subsample': 0.8}</t>
-  </si>
-  <si>
-    <t>{'model__colsample_bytree': 0.8, 'model__gamma': 0.1, 'model__learning_rate': 0.01, 'model__max_depth': 5, 'model__n_estimators': 100, 'model__subsample': 0.8}</t>
+    <t>{"model__C": 10}</t>
+  </si>
+  <si>
+    <t>{"model__n_neighbors": 9, "model__weights": "uniform"}</t>
+  </si>
+  <si>
+    <t>{"model__C": 0.1, "model__kernel": "linear"}</t>
+  </si>
+  <si>
+    <t>{"model__max_depth": 3, "model__min_samples_leaf": 1}</t>
+  </si>
+  <si>
+    <t>{"model__max_depth": 5, "model__min_samples_leaf": 4, "model__n_estimators": 300}</t>
+  </si>
+  <si>
+    <t>{"model__alpha": 1}</t>
+  </si>
+  <si>
+    <t>{"model__learning_rate": 0.1, "model__n_estimators": 250, "model__num_leaves": 31}</t>
+  </si>
+  <si>
+    <t>{"model__learning_rate": 0.03, "model__max_depth": 3, "model__n_estimators": 100}</t>
   </si>
 </sst>
 </file>
@@ -443,10 +452,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,210 +480,264 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
-        <v>0.7971311475409836</v>
-      </c>
-      <c r="C2">
-        <v>0.7972027972027972</v>
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>0.8475836431226765</v>
+        <v>368</v>
       </c>
       <c r="E2">
-        <v>0.8216216216216217</v>
+        <v>0.8614130434782609</v>
       </c>
       <c r="F2">
-        <v>0.8514538880684421</v>
+        <v>0.8844221105527639</v>
       </c>
       <c r="G2">
-        <v>0.1519081992227518</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="H2">
+        <v>0.8734491315136477</v>
+      </c>
+      <c r="I2">
+        <v>0.9224055475848877</v>
+      </c>
+      <c r="J2">
+        <v>0.1057997150135372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>0.7827868852459017</v>
-      </c>
-      <c r="C3">
-        <v>0.7781569965870307</v>
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>0.8475836431226765</v>
+        <v>368</v>
       </c>
       <c r="E3">
-        <v>0.8113879003558719</v>
+        <v>0.8586956521739131</v>
       </c>
       <c r="F3">
-        <v>0.8463444857496902</v>
+        <v>0.8877551020408163</v>
       </c>
       <c r="G3">
-        <v>0.1568685989322952</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="H3">
+        <v>0.87</v>
+      </c>
+      <c r="I3">
+        <v>0.9167264466762315</v>
+      </c>
+      <c r="J3">
+        <v>0.1132917337627483</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>0.7807377049180327</v>
-      </c>
-      <c r="C4">
-        <v>0.7892857142857143</v>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>0.8215613382899628</v>
+        <v>368</v>
       </c>
       <c r="E4">
-        <v>0.8051001821493625</v>
+        <v>0.8641304347826086</v>
       </c>
       <c r="F4">
-        <v>0.8589567313404967</v>
+        <v>0.8969072164948454</v>
       </c>
       <c r="G4">
-        <v>0.1482460864427534</v>
-      </c>
-      <c r="H4" t="s">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="H4">
+        <v>0.8743718592964824</v>
+      </c>
+      <c r="I4">
+        <v>0.9265004782400764</v>
+      </c>
+      <c r="J4">
+        <v>0.1041970820126365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>368</v>
+      </c>
+      <c r="E5">
+        <v>0.8152173913043478</v>
+      </c>
+      <c r="F5">
+        <v>0.84</v>
+      </c>
+      <c r="G5">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="H5">
+        <v>0.8316831683168316</v>
+      </c>
+      <c r="I5">
+        <v>0.8958034433285509</v>
+      </c>
+      <c r="J5">
+        <v>0.1260434435745349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>368</v>
+      </c>
+      <c r="E6">
+        <v>0.8722826086956522</v>
+      </c>
+      <c r="F6">
+        <v>0.8866995073891626</v>
+      </c>
+      <c r="G6">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="H6">
+        <v>0.8845208845208845</v>
+      </c>
+      <c r="I6">
+        <v>0.9353778096604495</v>
+      </c>
+      <c r="J6">
+        <v>0.1013101982415013</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>368</v>
+      </c>
+      <c r="E7">
+        <v>0.8668478260869565</v>
+      </c>
+      <c r="F7">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="G7">
+        <v>0.8578431372549019</v>
+      </c>
+      <c r="H7">
+        <v>0.8771929824561403</v>
+      </c>
+      <c r="I7">
+        <v>0.9224055475848876</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>368</v>
+      </c>
+      <c r="E8">
+        <v>0.8586956521739131</v>
+      </c>
+      <c r="F8">
+        <v>0.88</v>
+      </c>
+      <c r="G8">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="H8">
+        <v>0.8712871287128713</v>
+      </c>
+      <c r="I8">
+        <v>0.9215686274509804</v>
+      </c>
+      <c r="J8">
+        <v>0.1240755559546973</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>0.7766393442622951</v>
-      </c>
-      <c r="C5">
-        <v>0.7312138728323699</v>
-      </c>
-      <c r="D5">
-        <v>0.9405204460966543</v>
-      </c>
-      <c r="E5">
-        <v>0.8227642276422764</v>
-      </c>
-      <c r="F5">
-        <v>0.8530240532328428</v>
-      </c>
-      <c r="G5">
-        <v>0.1517119475144191</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>0.8155737704918032</v>
-      </c>
-      <c r="C6">
-        <v>0.7953795379537953</v>
-      </c>
-      <c r="D6">
-        <v>0.895910780669145</v>
-      </c>
-      <c r="E6">
-        <v>0.8426573426573427</v>
-      </c>
-      <c r="F6">
-        <v>0.8829420651491233</v>
-      </c>
-      <c r="G6">
-        <v>0.1419389174032027</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>0.7868852459016393</v>
-      </c>
-      <c r="C7">
-        <v>0.7815699658703071</v>
-      </c>
-      <c r="D7">
-        <v>0.8513011152416357</v>
-      </c>
-      <c r="E7">
-        <v>0.8149466192170819</v>
-      </c>
-      <c r="F7">
-        <v>0.8513350647587038</v>
-      </c>
-      <c r="H7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8">
-        <v>0.8155737704918032</v>
-      </c>
-      <c r="C8">
-        <v>0.8033898305084746</v>
-      </c>
-      <c r="D8">
-        <v>0.8810408921933085</v>
-      </c>
-      <c r="E8">
-        <v>0.8404255319148937</v>
-      </c>
-      <c r="F8">
-        <v>0.8808456824701668</v>
-      </c>
-      <c r="G8">
-        <v>0.137744761147548</v>
-      </c>
-      <c r="H8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9">
-        <v>0.7950819672131147</v>
-      </c>
-      <c r="C9">
-        <v>0.7734627831715211</v>
+      <c r="C9" t="s">
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>0.8884758364312267</v>
+        <v>368</v>
       </c>
       <c r="E9">
-        <v>0.8269896193771626</v>
+        <v>0.875</v>
       </c>
       <c r="F9">
-        <v>0.8764746821476466</v>
+        <v>0.883495145631068</v>
       </c>
       <c r="G9">
-        <v>0.160635571819733</v>
-      </c>
-      <c r="H9" t="s">
-        <v>23</v>
+        <v>0.8921568627450981</v>
+      </c>
+      <c r="H9">
+        <v>0.8878048780487805</v>
+      </c>
+      <c r="I9">
+        <v>0.9331659493065518</v>
+      </c>
+      <c r="J9">
+        <v>0.1016310590444923</v>
       </c>
     </row>
   </sheetData>
